--- a/out/Attention-mamba2_repeat_5_000006.xlsx
+++ b/out/Attention-mamba2_repeat_5_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.043559541701984</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002634754965268076</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3391134877834929</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6788687414089325</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07831524298898677</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2605347692979793</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2605347692979793</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2602574311995692</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8520424557693203</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.966039283598268</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1630287854889171</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.438810684578326</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2855603791223821</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.846982572791098</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1563832553197194</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.873942568515406</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06458836508999025</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.846572498973952</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08047205072216178</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.942938682639566</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.048454569299957</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.959321162250057</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03683849862515046</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.984522884970181</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01629296941965372</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.980239424368327</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01292890217836523</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.989797754569316</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006408795395114141</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.989678284239828</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003724595355897072</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.990715291940081</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001859797677948536</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.990707970141088</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009148874119621448</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.990679649521159</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005290244444644378</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.990822790660561</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001735576091177526</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.990639337197274</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.483164589084172e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.990635345041856</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.990638510200359</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.990631882207618</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.990632800443763</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.990625798152942</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.990621936077846</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.990617388765661</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.990617478710311</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.990616620776726</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.990616849097761</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.990616053433549</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.990616115702922</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.990616143378199</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.990616295592222</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.99061594965126</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.990616025758272</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.990616191809934</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.990616551588533</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.990616572344991</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.99061667612728</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.990616904448315</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.990616779909568</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.990616807584845</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.990616862935399</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.99061712585053</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.990617042824699</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.990616835260122</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.990616849097761</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.990616987474145</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.990616703802557</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.990616530832076</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.990616427049788</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.990616572344991</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.990616814503665</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.990616641533184</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.990616344023957</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.990616330186318</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.990615963488899</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.990615963488899</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.990615901219526</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.990615797437237</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.990615624466756</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.990615672898491</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.990615313119891</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.990615271606976</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.99061532695753</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.990615382308084</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.990615423820999</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.990615153987049</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.990615209337602</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.990615354632806</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.99061532003871</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.990615306201072</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.990615396145722</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.990615714411406</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.990615534522106</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.990615576035022</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.990615389226903</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.990615458415095</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.990615257769337</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.990615299282253</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.99061532695753</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000006.xlsx
+++ b/out/Attention-mamba2_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.3801101738204643</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002634754965268076</v>
+        <v>-0.0001316087314775214</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3391134877834929</v>
+        <v>0.1693904787762179</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6788687414089325</v>
+        <v>0.3391019477042859</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07831524298898677</v>
+        <v>-0.03911932125401667</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2605347692979793</v>
+        <v>0.1301395487907238</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2605347692979793</v>
+        <v>0.1301395487907238</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2602574311995692</v>
+        <v>0.1300003091722</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8520424557693203</v>
+        <v>0.427774221362923</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.443559541701984</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.966039283598268</v>
+        <v>0.9864005503555625</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1630287854889171</v>
+        <v>0.08184971514928836</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.424137072939437</v>
+        <v>-0.5801101738204644</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.438810684578326</v>
+        <v>0.7217016308981241</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2855603791223821</v>
+        <v>0.1433675385545866</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.07536333809757498</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.846982572791098</v>
+        <v>0.9266274263058012</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1563832553197194</v>
+        <v>0.07851351960461012</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757498</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.873942568515406</v>
+        <v>0.9401629173563815</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06458836508999025</v>
+        <v>0.03242703020031133</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.846572498973952</v>
+        <v>0.9264215455072827</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.08047205072216178</v>
+        <v>0.04040178734942915</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.942938682639566</v>
+        <v>0.9748031391810468</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.048454569299957</v>
+        <v>0.02432650418635402</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.959321162250057</v>
+        <v>0.9830281257362696</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03683849862515046</v>
+        <v>0.01849558085133828</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.984522884970181</v>
+        <v>0.9956812065500684</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01629296941965372</v>
+        <v>0.008178264845579323</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757492</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.980239424368327</v>
+        <v>0.9935282213292671</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01292890217836523</v>
+        <v>0.006487173207315154</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.07536333809757492</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.989797754569316</v>
+        <v>0.9983244697102194</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006408795395114141</v>
+        <v>0.003214405098873595</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.5801101738204644</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.989678284239828</v>
+        <v>0.9982619905629461</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003724595355897072</v>
+        <v>0.001868525280185424</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.043559541701984</v>
+        <v>-1.235583685738504</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.990715291940081</v>
+        <v>0.9987804328086265</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001859797677948536</v>
+        <v>0.0009317626400927121</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.043559541701984</v>
+        <v>-0.5801101738204644</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.990707970141088</v>
+        <v>0.9987742664759031</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009148874119621448</v>
+        <v>0.0004578183541434541</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8241370729394373</v>
+        <v>-0.5801101738204645</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.990679649521159</v>
+        <v>0.9987575506941562</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005290244444644378</v>
+        <v>0.0002620122222322189</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.043559541701984</v>
+        <v>0.07536333809757491</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.990822790660561</v>
+        <v>0.9988268530443015</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001735576091177526</v>
+        <v>8.427880455887632e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.424137072939437</v>
+        <v>0.275363338097575</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.990639337197274</v>
+        <v>0.9987320728071197</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.483164589084172e-05</v>
+        <v>3.991582294542086e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.990635345041856</v>
+        <v>0.9987275836482297</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>1.946196130108506e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.990638510200359</v>
+        <v>0.99872676655036</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>6.850902234816308e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.990631882207618</v>
+        <v>0.9987209145004837</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.990632800443763</v>
+        <v>0.9987191416414306</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.990625798152942</v>
+        <v>0.9987131421078339</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.990621936077846</v>
+        <v>0.9987088994976799</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.990617388765661</v>
+        <v>0.9987091278187146</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.424137072939437</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.990617478710311</v>
+        <v>0.9987092177633645</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.9308368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.990616620776726</v>
+        <v>0.9987083598297797</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.990616849097761</v>
+        <v>0.9987085881508144</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.990616053433549</v>
+        <v>0.9987077924866027</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.990616115702922</v>
+        <v>0.9987078547559758</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.990616143378199</v>
+        <v>0.9987078824312526</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.990616295592222</v>
+        <v>0.9987080346452759</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.99061594965126</v>
+        <v>0.9987076887043141</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.990616025758272</v>
+        <v>0.9987077648113258</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.990616191809934</v>
+        <v>0.9987079308629874</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.990616551588533</v>
+        <v>0.9987082906415875</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.990616572344991</v>
+        <v>0.9987083113980452</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.99061667612728</v>
+        <v>0.9987084151803337</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.990616904448315</v>
+        <v>0.9987086435013683</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.990616779909568</v>
+        <v>0.9987085189626221</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.990616807584845</v>
+        <v>0.998708546637899</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.990616862935399</v>
+        <v>0.9987086019884529</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.99061712585053</v>
+        <v>0.9987088649035837</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.990617042824699</v>
+        <v>0.9987087818777528</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.990616835260122</v>
+        <v>0.9987085743131761</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.990616849097761</v>
+        <v>0.9987085881508144</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.990616987474145</v>
+        <v>0.9987087265271991</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.990616703802557</v>
+        <v>0.9987084428556106</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.990616530832076</v>
+        <v>0.9987082698851297</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.990616427049788</v>
+        <v>0.9987081661028413</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.990616572344991</v>
+        <v>0.9987083113980452</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.990616814503665</v>
+        <v>0.9987085535567184</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.990616641533184</v>
+        <v>0.9987083805862375</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.990616344023957</v>
+        <v>0.9987080830770104</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.990616330186318</v>
+        <v>0.9987080692393719</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.990615963488899</v>
+        <v>0.9987077025419527</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.990615963488899</v>
+        <v>0.9987077025419527</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.990615901219526</v>
+        <v>0.9987076402725796</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.990615797437237</v>
+        <v>0.9987075364902911</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.990615624466756</v>
+        <v>0.9987073635198104</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.990615672898491</v>
+        <v>0.9987074119515449</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.990615313119891</v>
+        <v>0.9987070521729449</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.990615271606976</v>
+        <v>0.9987070106600295</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.99061532695753</v>
+        <v>0.9987070660105832</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.990615382308084</v>
+        <v>0.9987071213611372</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.990615423820999</v>
+        <v>0.9987071628740525</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.990615153987049</v>
+        <v>0.9987068930401024</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.990615209337602</v>
+        <v>0.9987069483906564</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.990615354632806</v>
+        <v>0.9987070936858603</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.99061532003871</v>
+        <v>0.998707059091764</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.990615306201072</v>
+        <v>0.9987070452541255</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.990615396145722</v>
+        <v>0.9987071351987756</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.990615714411406</v>
+        <v>0.9987074534644603</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.990615534522106</v>
+        <v>0.9987072735751602</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.990615576035022</v>
+        <v>0.9987073150880755</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.990615389226903</v>
+        <v>0.9987071282799563</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.990615458415095</v>
+        <v>0.9987071974681487</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.990615257769337</v>
+        <v>0.9987069968223909</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.990615299282253</v>
+        <v>0.9987070383353064</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8241370729394373</v>
+        <v>0.7308368500156143</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.99061532695753</v>
+        <v>0.9987070660105832</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000006.xlsx
+++ b/out/Attention-mamba2_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.3879025876522064</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3312513530254364</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.3571824431419373</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.3788868188858032</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.3494741320610046</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3575290143489838</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.3008823990821838</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.3845632970333099</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.3778353035449982</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.3430309891700745</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.2914301753044128</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2609568238258362</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.3343006670475006</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2638359367847443</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.2641067504882812</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2674961984157562</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.3017770648002625</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.3462140560150146</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.385758101940155</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.3353487849235535</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.3166972398757935</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2640019059181213</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.2935563623905182</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.3649974167346954</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2986508309841156</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.4194192290306091</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2509708106517792</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.303022712469101</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2879577577114105</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2749987542629242</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.23819699883461</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2294576168060303</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.2599874138832092</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.2885758280754089</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.235583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.2943408191204071</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.294574499130249</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2951464653015137</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2731736898422241</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.2996333241462708</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.3278486132621765</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.2730276584625244</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.05847776681184769</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3801101738204643</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02546241134405136</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.275363338097575</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001316087314775214</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1693904787762179</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01317015662789345</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3391019477042859</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.03911932125401667</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.006849363446235657</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1301395487907238</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.03788615763187408</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1301395487907238</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.05597225949168205</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.275363338097575</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1300003091722</v>
+        <v>0.2121828056220904</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.427774221362923</v>
+        <v>0.6424215629474357</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.02145686745643616</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.275363338097575</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9864005503555625</v>
+        <v>1.498305468185155</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.08184971514928836</v>
+        <v>0.1229201274863253</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.05728202685713768</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5801101738204644</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7217016308981241</v>
+        <v>1.100786471017579</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1433675385545866</v>
+        <v>0.2153064783390107</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01784644275903702</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.07536333809757498</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9266274263058012</v>
+        <v>1.408539430577886</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.07851351960461012</v>
+        <v>0.1179096626694459</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.000728897750377655</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.07536333809757498</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9401629173563815</v>
+        <v>1.42886669640263</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.03242703020031133</v>
+        <v>0.0486982110234413</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.03069782629609108</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9264215455072827</v>
+        <v>1.408230243696448</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.04040178734942915</v>
+        <v>0.06067379193630498</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01965194940567017</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9748031391810468</v>
+        <v>1.480888378421932</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.02432650418635402</v>
+        <v>0.03653405071541295</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.08394639194011688</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.275363338097575</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9830281257362696</v>
+        <v>1.493240533225513</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01849558085133828</v>
+        <v>0.02777569992871883</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-4.809349775314331e-05</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.275363338097575</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9956812065500684</v>
+        <v>1.512242270920735</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.008178264845579323</v>
+        <v>0.01228340625092626</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.08943851292133331</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.07536333809757492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.9935282213292671</v>
+        <v>1.509011539618106</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.006487173207315154</v>
+        <v>0.009745870870039001</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.08257316052913666</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.07536333809757492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9983244697102194</v>
+        <v>1.516217269789167</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.003214405098873595</v>
+        <v>0.004830361348968655</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.03851811587810516</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5801101738204644</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9982619905629461</v>
+        <v>1.516125949833449</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001868525280185424</v>
+        <v>0.002808197121023766</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.06459686905145645</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.235583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9987804328086265</v>
+        <v>1.516906926000488</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0009317626400927121</v>
+        <v>0.001400143960139068</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0230129137635231</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5801101738204644</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9987742664759031</v>
+        <v>1.516900176501404</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0004578183541434541</v>
+        <v>0.000690664855296372</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.02574771642684937</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5801101738204645</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9987575506941562</v>
+        <v>1.516877566444368</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002620122222322189</v>
+        <v>0.0003988559861262311</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.009074307978153229</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.07536333809757491</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9988268530443015</v>
+        <v>1.516984247613119</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.427880455887632e-05</v>
+        <v>0.0001289182068383145</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.05293067172169685</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.275363338097575</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9987320728071197</v>
+        <v>1.516845130762884</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.991582294542086e-05</v>
+        <v>6.23737344181313e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.05130110308527946</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9987275836482297</v>
+        <v>1.516840890105731</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.946196130108506e-05</v>
+        <v>3.169294195162759e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.06847834587097168</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.99872676655036</v>
+        <v>1.516842064136047</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>6.850902234816308e-06</v>
+        <v>1.396144357570609e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.06726612895727158</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9987209145004837</v>
+        <v>1.516835822627464</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0474187470972538</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9987191416414306</v>
+        <v>1.51683512548206</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.06752526760101318</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9987131421078339</v>
+        <v>1.516828790621513</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0522761270403862</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9987088994976799</v>
+        <v>1.516824548011359</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0719200000166893</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9987091278187146</v>
+        <v>1.516824776332394</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.06050537899136543</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9987092177633645</v>
+        <v>1.516824866277044</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.07321172207593918</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9987083598297797</v>
+        <v>1.516824008343459</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.05905848741531372</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9987085881508144</v>
+        <v>1.516824236664494</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.05173056572675705</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9987077924866027</v>
+        <v>1.516823441000282</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.07368491590023041</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9987078547559758</v>
+        <v>1.516823503269655</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.07041311264038086</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9987078824312526</v>
+        <v>1.516823530944932</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.06282882392406464</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9987080346452759</v>
+        <v>1.516823683158955</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.07202917337417603</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9987076887043141</v>
+        <v>1.516823337217993</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.06622955203056335</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9987077648113258</v>
+        <v>1.516823413325005</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.07045166194438934</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9987079308629874</v>
+        <v>1.516823579376666</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.06879911571741104</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9987082906415875</v>
+        <v>1.516823939155266</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.06555306911468506</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9987083113980452</v>
+        <v>1.516823959911724</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05759547650814056</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9987084151803337</v>
+        <v>1.516824063694012</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.07195599377155304</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9987086435013683</v>
+        <v>1.516824292015047</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.06797024607658386</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9987085189626221</v>
+        <v>1.516824167476301</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.07112105190753937</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.998708546637899</v>
+        <v>1.516824195151578</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.06307682394981384</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9987086019884529</v>
+        <v>1.516824250502132</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.07253403216600418</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9987088649035837</v>
+        <v>1.516824513417263</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.06916732341051102</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9987087818777528</v>
+        <v>1.516824430391432</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.06877661496400833</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9987085743131761</v>
+        <v>1.516824222826855</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06725182384252548</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9987085881508144</v>
+        <v>1.516824236664494</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.06761039793491364</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9987087265271991</v>
+        <v>1.516824375040878</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.06657759100198746</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9987084428556106</v>
+        <v>1.516824091369289</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.06797614693641663</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9987082698851297</v>
+        <v>1.516823918398809</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.06529465317726135</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9987081661028413</v>
+        <v>1.51682381461652</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.06713796406984329</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9987083113980452</v>
+        <v>1.516823959911724</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.06566343456506729</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9987085535567184</v>
+        <v>1.516824202070397</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.06454792618751526</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9987083805862375</v>
+        <v>1.516824029099917</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.06556212902069092</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9987080830770104</v>
+        <v>1.51682373159069</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.06330104917287827</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9987080692393719</v>
+        <v>1.516823717753051</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.06344403326511383</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9987077025419527</v>
+        <v>1.516823351055631</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.06751246005296707</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9987077025419527</v>
+        <v>1.516823351055631</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.06204088032245636</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9987076402725796</v>
+        <v>1.516823288786258</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.06834101676940918</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9987075364902911</v>
+        <v>1.51682318500397</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.06119412928819656</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9987073635198104</v>
+        <v>1.516823012033489</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.06358388066291809</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9987074119515449</v>
+        <v>1.516823060465224</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06110838055610657</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9987070521729449</v>
+        <v>1.516822700686624</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.05830109491944313</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9987070106600295</v>
+        <v>1.516822659173708</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.05851639807224274</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9987070660105832</v>
+        <v>1.516822714524262</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.05501268059015274</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9987071213611372</v>
+        <v>1.516822769874816</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.05346234887838364</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9987071628740525</v>
+        <v>1.516822811387732</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.05232903361320496</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9987068930401024</v>
+        <v>1.516822541553781</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0519903376698494</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9987069483906564</v>
+        <v>1.516822596904335</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.05190431326627731</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9987070936858603</v>
+        <v>1.516822742199539</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.05126871913671494</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7308368500156143</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.998707059091764</v>
+        <v>1.516822707605443</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.05570387095212936</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9987070452541255</v>
+        <v>1.516822693767805</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.07474417239427567</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9987071351987756</v>
+        <v>1.516822783712455</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05215639993548393</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9987074534644603</v>
+        <v>1.516823101978139</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.07872168719768524</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9987072735751602</v>
+        <v>1.516822922088839</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.07048091292381287</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9987073150880755</v>
+        <v>1.516822963601755</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.06468349695205688</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9987071282799563</v>
+        <v>1.516822776793636</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.06322352588176727</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9987071974681487</v>
+        <v>1.516822845981827</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.06087791547179222</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9987069968223909</v>
+        <v>1.51682264533607</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.05903820693492889</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9987070383353064</v>
+        <v>1.516822686848986</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.07725372910499573</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7308368500156143</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9987070660105832</v>
+        <v>1.516822714524262</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000006.xlsx
+++ b/out/Attention-mamba2_repeat_5_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.3879025876522064</v>
+        <v>-0.3879023790359497</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3312513530254364</v>
+        <v>-0.3312512040138245</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.3571824431419373</v>
+        <v>-0.3571822047233582</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.3788868188858032</v>
+        <v>-0.3788867592811584</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.3494741320610046</v>
+        <v>-0.3494738638401031</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3575290143489838</v>
+        <v>-0.3575287759304047</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.3008823990821838</v>
+        <v>-0.3008823692798615</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.3845632970333099</v>
+        <v>-0.3845632076263428</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.3778353035449982</v>
+        <v>-0.3778351843357086</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.3430309891700745</v>
+        <v>-0.3430308699607849</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.2914301753044128</v>
+        <v>-0.2914302051067352</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2609568238258362</v>
+        <v>-0.2609566748142242</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.3343006670475006</v>
+        <v>-0.3343008458614349</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2638359367847443</v>
+        <v>-0.2638356387615204</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.2641067504882812</v>
+        <v>-0.2641063928604126</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2674961984157562</v>
+        <v>-0.2674959301948547</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.3017770648002625</v>
+        <v>-0.3017768561840057</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.3462140560150146</v>
+        <v>-0.3462139070034027</v>
       </c>
       <c r="JB19" t="n">
         <v>0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.385758101940155</v>
+        <v>-0.3857579827308655</v>
       </c>
       <c r="JB20" t="n">
         <v>0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.3353487849235535</v>
+        <v>-0.3353486657142639</v>
       </c>
       <c r="JB21" t="n">
         <v>0.16</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.3166972398757935</v>
+        <v>-0.3166976273059845</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2640019059181213</v>
+        <v>-0.2640017867088318</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.2935563623905182</v>
+        <v>-0.2935562133789062</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2986508309841156</v>
+        <v>-0.2986505627632141</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.4194192290306091</v>
+        <v>-0.4194191992282867</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2509708106517792</v>
+        <v>-0.2509706318378448</v>
       </c>
       <c r="JB28" t="n">
         <v>0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.303022712469101</v>
+        <v>-0.3030226826667786</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2879577577114105</v>
+        <v>-0.2879576086997986</v>
       </c>
       <c r="JB30" t="n">
         <v>0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2749987542629242</v>
+        <v>-0.2749984860420227</v>
       </c>
       <c r="JB31" t="n">
         <v>0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.23819699883461</v>
+        <v>-0.2381969094276428</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2294576168060303</v>
+        <v>-0.2294575273990631</v>
       </c>
       <c r="JB33" t="n">
         <v>0.8599999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.2599874138832092</v>
+        <v>-0.2599873542785645</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.2885758280754089</v>
+        <v>-0.2885755598545074</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.2943408191204071</v>
+        <v>-0.2943406701087952</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.294574499130249</v>
+        <v>-0.2945743501186371</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2951464653015137</v>
+        <v>-0.2951464056968689</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2731736898422241</v>
+        <v>-0.2731736302375793</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.2996333241462708</v>
+        <v>-0.2996332049369812</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.3278486132621765</v>
+        <v>-0.327848494052887</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.1600000000000001</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.2730276584625244</v>
+        <v>-0.2730274498462677</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.05847776681184769</v>
+        <v>-0.058477483689785</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.02546241134405136</v>
+        <v>0.02546239644289017</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01317015662789345</v>
+        <v>0.01317019388079643</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.006849363446235657</v>
+        <v>0.006849423050880432</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.03788615763187408</v>
+        <v>0.03788618743419647</v>
       </c>
       <c r="JB47" t="n">
         <v>0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.05597225949168205</v>
+        <v>0.05597241967916489</v>
       </c>
       <c r="JB48" t="n">
         <v>0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.02145686745643616</v>
+        <v>-0.02145712077617645</v>
       </c>
       <c r="JB49" t="n">
         <v>0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.05728202685713768</v>
+        <v>0.05728217959403992</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.01784644275903702</v>
+        <v>-0.01784666627645493</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.16</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.000728897750377655</v>
+        <v>0.0007287636399269104</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.03069782629609108</v>
+        <v>0.03069761767983437</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.01965194940567017</v>
+        <v>0.01965173706412315</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.08394639194011688</v>
+        <v>0.08394627273082733</v>
       </c>
       <c r="JB55" t="n">
         <v>0.2599999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-4.809349775314331e-05</v>
+        <v>-4.831701517105103e-05</v>
       </c>
       <c r="JB56" t="n">
         <v>0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.08943851292133331</v>
+        <v>0.08943849056959152</v>
       </c>
       <c r="JB57" t="n">
         <v>0.8599999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.08257316052913666</v>
+        <v>0.08257327973842621</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.06459686905145645</v>
+        <v>-0.064596988260746</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0230129137635231</v>
+        <v>-0.02301301807165146</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.02574771642684937</v>
+        <v>0.02574767917394638</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.009074307978153229</v>
+        <v>-0.009074389934539795</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.05293067172169685</v>
+        <v>0.05293067544698715</v>
       </c>
       <c r="JB64" t="n">
         <v>0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.05130110308527946</v>
+        <v>0.0513010211288929</v>
       </c>
       <c r="JB65" t="n">
         <v>0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.06847834587097168</v>
+        <v>0.06847824901342392</v>
       </c>
       <c r="JB66" t="n">
         <v>0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.06726612895727158</v>
+        <v>0.06726617366075516</v>
       </c>
       <c r="JB67" t="n">
         <v>0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0474187470972538</v>
+        <v>0.04741867631673813</v>
       </c>
       <c r="JB68" t="n">
         <v>0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.06752526760101318</v>
+        <v>0.06752526015043259</v>
       </c>
       <c r="JB69" t="n">
         <v>0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.0522761270403862</v>
+        <v>0.05227617919445038</v>
       </c>
       <c r="JB70" t="n">
         <v>0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.06050537899136543</v>
+        <v>0.06050530821084976</v>
       </c>
       <c r="JB72" t="n">
         <v>0.1199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.05173056572675705</v>
+        <v>0.05173048004508018</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.07368491590023041</v>
+        <v>0.07368481159210205</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.02000000000000007</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.07041311264038086</v>
+        <v>0.07041315734386444</v>
       </c>
       <c r="JB77" t="n">
         <v>0.1199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.06282882392406464</v>
+        <v>0.06282876431941986</v>
       </c>
       <c r="JB78" t="n">
         <v>0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.07202917337417603</v>
+        <v>0.07202915847301483</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.06622955203056335</v>
+        <v>0.06622953712940216</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.07045166194438934</v>
+        <v>0.07045172899961472</v>
       </c>
       <c r="JB81" t="n">
         <v>0.1199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.06879911571741104</v>
+        <v>0.06879901885986328</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.06555306911468506</v>
+        <v>0.06555313616991043</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05759547650814056</v>
+        <v>0.05759548395872116</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.06797024607658386</v>
+        <v>0.06797023862600327</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.07112105190753937</v>
+        <v>0.07112108170986176</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.07253403216600418</v>
+        <v>0.07253396511077881</v>
       </c>
       <c r="JB89" t="n">
         <v>0.5799999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.06916732341051102</v>
+        <v>0.06916731595993042</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.06877661496400833</v>
+        <v>0.06877655535936356</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06725182384252548</v>
+        <v>0.06725181639194489</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.06761039793491364</v>
+        <v>0.06761045008897781</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.06797614693641663</v>
+        <v>0.06797610223293304</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.06529465317726135</v>
+        <v>0.06529463827610016</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.06713796406984329</v>
+        <v>0.06713791936635971</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.06566343456506729</v>
+        <v>0.06566342711448669</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.06454792618751526</v>
+        <v>0.06454779952764511</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.06556212902069092</v>
+        <v>0.06556208431720734</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.06330104917287827</v>
+        <v>0.06330098211765289</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.06344403326511383</v>
+        <v>0.06344404071569443</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.06751246005296707</v>
+        <v>0.06751248240470886</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.06204088032245636</v>
+        <v>0.06204073876142502</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.06834101676940918</v>
+        <v>0.06834103912115097</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.06119412928819656</v>
+        <v>0.06119413673877716</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.3</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.06358388066291809</v>
+        <v>0.06358384341001511</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06110838055610657</v>
+        <v>0.06110836192965508</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.3</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.05830109491944313</v>
+        <v>0.05830113589763641</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.05851639807224274</v>
+        <v>0.05851641297340393</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.05346234887838364</v>
+        <v>0.05346236377954483</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.05232903361320496</v>
+        <v>0.05232901871204376</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0519903376698494</v>
+        <v>0.05199034512042999</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.05190431326627731</v>
+        <v>0.05190427601337433</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.05126871913671494</v>
+        <v>0.05126873403787613</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.5799999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.05570387095212936</v>
+        <v>0.05570382624864578</v>
       </c>
       <c r="JB117" t="n">
         <v>0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.07474417239427567</v>
+        <v>0.07474413514137268</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.05215639993548393</v>
+        <v>0.05215643718838692</v>
       </c>
       <c r="JB119" t="n">
         <v>0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.07872168719768524</v>
+        <v>0.07872174680233002</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.07048091292381287</v>
+        <v>0.07048092782497406</v>
       </c>
       <c r="JB121" t="n">
         <v>0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.06468349695205688</v>
+        <v>0.06468347460031509</v>
       </c>
       <c r="JB122" t="n">
         <v>0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.06322352588176727</v>
+        <v>0.06322349607944489</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.06087791547179222</v>
+        <v>0.06087794154882431</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.05903820693492889</v>
+        <v>0.0590382032096386</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5800000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.07725372910499573</v>
+        <v>0.0772537961602211</v>
       </c>
       <c r="JB126" t="n">
         <v>0.72</v>
